--- a/data/daily/2026-09/2026-09-28.xlsx
+++ b/data/daily/2026-09/2026-09-28.xlsx
@@ -1170,14 +1170,114 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1292,92 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,167 +1392,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1400,214 +1425,239 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2519,7 +2569,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 8입(7+1) - 추석 기프트 에디션 (공식수입)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 8입(7+1) - 스페셜 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2546,23 +2596,11 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16143</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>선물용으로 높은 만족도 — 명절이나 생일 선물로 주고받기에 매우 적절함</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>우수한 피로 회복 효과 — 섭취 후 피로가 해소되고 체력이 보충되는 느낌을 받음</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>신속한 배송 서비스 — 주문 후 배송이 빠르게 진행되어 만족스러움</t>
-        </is>
-      </c>
+        <v>16145</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -2607,21 +2645,9 @@
       <c r="J3" t="n">
         <v>15477</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>피로 회복 및 활력 증진 — 피곤할 때 먹으면 체력이 회복되고 활력이 생김</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>고급스러운 포장 디자인 — 포장과 패키지가 예쁘고 고급스러워 선물용으로 적합함</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>간편한 휴대 및 섭취 — 하나씩 들고 다니며 부담 없이 먹기 편리함</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -2664,24 +2690,12 @@
         <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>3369</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>체력 보충 및 피로 개선 — 마시고 나면 피로가 줄고 일상에 활력이 생김</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>쿠폰 적용을 통한 할인 — 할인 쿠폰을 활용하여 합리적인 가격에 구매함</t>
-        </is>
-      </c>
+        <v>3370</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>동봉 쇼핑백 상태 불량 — 함께 제공된 선물용 쇼핑백이 훼손되어 도착함</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -2725,22 +2739,10 @@
       <c r="J5" t="n">
         <v>796</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>체력 유지 및 피로 회복 — 활동량이 많거나 육아 시 섭취하면 체력 유지에 큰 도움이 됨</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>편리한 개별 포장 방식 — 한 포씩 포장되어 가방이나 책상에 두고 챙겨 먹기 용이함</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>배송 요청사항 미반영 — 관리실 위탁 요청에도 불구하고 문 앞에 배송되어 아쉬움</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
@@ -2782,23 +2784,11 @@
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>1691</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>품격 있는 고급 포장 — 패키지와 용기 포장이 품격 있어서 선물받을 때 기분이 좋음</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>액상형의 편리한 섭취 — 액상 제형으로 알약보다 마시기 편리함</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>빠른 피로 회복 효과 — 복용 시 피로가 풀리고 일상 에너지 보충에 효과적임</t>
-        </is>
-      </c>
+        <v>1693</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -2843,27 +2833,11 @@
       <c r="J7" t="n">
         <v>214</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>피로 개선 및 활력 보충 — 꾸준히 섭취하면 피로가 덜하고 활력 체감에 도움이 됨</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>정성스러운 선물 패키징 — 패키지 구성이 정성스러워 생일이나 명절 선물용으로 만족함</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>상자 및 쇼핑백 오염 — 배송된 상자와 쇼핑백에 먼지가 가득 묻어 손질이 필요함</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>봉인 스티커 훼손 문제 — 밀봉 스티커가 반쯤 떼어져 있고 손자국과 이물질이 묻어 있음</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
@@ -2904,23 +2878,11 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>8729</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>물 없이 간편한 섭취 — 액상과 정제가 함께 있어 물 없이도 간편하게 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>에너지 충전과 상큼한 맛 — 오렌지 맛으로 맛있으며 섭취 후 에너지가 생김</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>깔끔하고 예쁜 패키지 — 포장 케이스와 패키지가 예뻐 선물용으로 만족도가 높음</t>
-        </is>
-      </c>
+        <v>8728</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -2956,7 +2918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260601193534_8d89165f65364cb0b3c77a98481c17d6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260928130637_4b5e189e4cc74b40bc33bd3c75d10253.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -2965,21 +2927,9 @@
       <c r="J9" t="n">
         <v>779</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>넉넉한 용량과 알찬 구성 — 한 달 동안 먹을 수 있는 넉넉한 수량과 구성이 만족스러움</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>선물용 쇼핑백 기본 제공 — 쇼핑백이 함께 포함되어 명절 선물로 전달하기 용이함</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>빠른 배송 서비스 — 연휴 기간임에도 차질 없이 빠르게 배송됨</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -3024,21 +2974,9 @@
       <c r="J10" t="n">
         <v>6489</v>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>맛있는 구미 젤리 제형 — 마이구미처럼 맛있고 쫄깃한 젤리라 거부감 없이 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>물 없이 편리한 섭취 — 알약을 잘 못 먹는 사람도 물 없이 편하게 챙겨 먹음</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>귀엽고 깔끔한 포장 — 포장이 귀엽고 깔끔하여 부담 없이 선물하기에 적합함</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -3083,22 +3021,10 @@
       <c r="J11" t="n">
         <v>772</v>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>남녀 맞춤 옵션 선택 — 바이탈 m/f 중 성별에 맞게 선택할 수 있어 유용함</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>꾸준한 활력 유지 효과 — 꾸준히 복용 시 피로가 줄고 활력이 오래 유지됨</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>알약 크기로 인한 목넘김 — 기존 제품에 비해 알약 크기가 다소 커서 삼키기 부담스러움</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -3142,22 +3068,10 @@
       <c r="J12" t="n">
         <v>745</v>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>고급스러운 포장 디자인 — 보자기, 틴케이스 등 고급스러운 포장으로 선물 가치가 높음</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>비리지 않고 맛있는 풍미 — 콜라겐 특유의 비린 맛이 전혀 없고 맛있게 먹을 수 있음</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>다소 높은 가격대 — 가격이 비싼 편이며 꾸준히 인상되어 구매 부담이 있음</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
     </row>
@@ -3199,23 +3113,11 @@
         <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>1679</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>속이 편안한 소화 개선 — 식후 복용 시 속이 편안해지고 소화 및 배변에 도움이 됨</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>고소하고 부담 없는 맛 — 고구마 맛 등으로 거부감 없이 맛있게 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>다양한 증정품과 혜택 — 라이브 방송 구매 시 사은품 구성과 가격 혜택이 우수함</t>
-        </is>
-      </c>
+        <v>1680</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -3258,24 +3160,12 @@
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>103</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>식후 더부룩함 완화 — 식사 후 복용하면 더부룩한 속이 가라앉고 편안해짐</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>고소하고 맛있는 말차 맛 — 말차 맛이 고소하고 맛있어서 매일 챙겨 먹기 수월함</t>
-        </is>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>다소 느린 배송 처리 — 주문 후 배송받기까지 시간이 다소 걸려 아쉬움</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
@@ -3290,50 +3180,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
+          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>28,900원</t>
+          <t>45,800원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>215</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>비리지 않고 달콤한 맛 — 단백질 음료 특유의 비린 맛과 텁텁함이 없고 달콤함</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>운동 후 든든한 포만감 — 운동 후 섭취 시 영양 보충과 함께 가볍게 허기를 달래줌</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>휴대하기 편한 슬림 용기 — 슬림한 팩 형태로 가방에 넣고 다니며 마시기 편함</t>
-        </is>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -3341,7 +3219,7 @@
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3349,58 +3227,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>아일로 타입1 콜라겐 비오틴 앰플 14일분 오간자 에디션 (고급 오간자 패키징 + 선물용 쇼핑백)</t>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>32,900원</t>
+          <t>28,900원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965673</t>
+          <t>https://gift.kakao.com/product/13550266</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260928091204_17479341408f44afb805d97625daff01.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>759</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>화려하고 고급스러운 포장 — 오간자 패키지와 디자인이 고급스러워 선물받을 때 기분이 좋음</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>상큼하고 부담 없는 맛 — 새콤상큼한 맛으로 맛에 대한 거부감 없이 마시기 좋음</t>
-        </is>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>단기 복용 시 미미한 효과 — 단기간 섭취로는 피부 효과를 즉각 느끼기 어려움</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3408,50 +3274,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>25,900원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12064702</t>
+          <t>https://gift.kakao.com/product/7556791</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>17</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>우수한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 숙취와 무거운 컨디션이 개선됨</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>간편한 스틱형 휴대성 — 물 없이 바로 먹는 스틱 포장이라 외출 시 지참하기 편함</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>고급스러운 보라색 포장 — 패키지 포장이 고급스러워 지인 선물용으로 적합함</t>
-        </is>
-      </c>
+        <v>1534</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -3467,50 +3321,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[좋은 아침 선물] 진저샷 미니보틀 8개입 (메시지 참 증정)</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>타이거모닝</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>29,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13586002</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260512190926_6c62df625cf44ea9ad3d7797fa43588b.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>11</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>아침 활력과 에너지 충전 — 공복이나 아침 섭취 시 눈이 뜨이고 피로가 가시는 느낌을 받음</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>과일이 들어간 상큼한 맛 — 과일 성분이 함유되어 생강 특유의 강한 맛없이 상큼하게 마심</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>귀여운 미니 보틀 용기 — 용기 병이 작고 귀여워 손이 잘 가고 기분 전환에 도움 됨</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -3518,7 +3360,7 @@
     <row r="19" ht="38" customHeight="1">
       <c r="B19" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3526,50 +3368,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>아일로 타입1 콜라겐 비오틴 앰플 14일분 오간자 에디션 (고급 오간자 패키징 + 선물용 쇼핑백)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>32,900원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7556791</t>
+          <t>https://gift.kakao.com/product/4965673</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260928091204_17479341408f44afb805d97625daff01.jpg</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>1534</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>아르기닌 밀크씨슬 조합 — 활력과 간 건강을 동시에 챙길 수 있는 2개월 세트 구성임</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>체감되는 활력 증진 효과 — 아침 일어날 때 컨디션이 가볍고 운동 시 집중력이 좋아짐</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>선물용 쇼핑백 증정 — 쇼핑백이 기본 동봉되어 주변에 선물하기에 용이함</t>
-        </is>
-      </c>
+        <v>759</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -3577,7 +3407,7 @@
     <row r="20" ht="38" customHeight="1">
       <c r="B20" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3585,50 +3415,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+          <t>[좋은 아침 선물] 진저샷 미니보틀 8개입 (메시지 참 증정)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>타이거모닝</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>43,900원</t>
+          <t>29,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7417420</t>
+          <t>https://gift.kakao.com/product/13586002</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260512190926_6c62df625cf44ea9ad3d7797fa43588b.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>248</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>6200mg 초고함량 활력 — 고함량 섭취로 운동 퍼포먼스 향상과 활력 유지에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>간편한 하루 1포 포장 — 개별 포장된 스틱 제형이라 언제든 들고 다니며 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>고급스러운 전용 쇼핑백 — 블랙과 레드 디자인 및 전용 쇼핑백이 제공되어 선물용으로 우수함</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
@@ -3673,21 +3491,9 @@
       <c r="J21" t="n">
         <v>15</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>12종의 알찬 종합 구성 — 드링크, 쿠키, 바 등 베스트 12종을 다양하게 체험할 수 있음</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>달콤하고 맛있는 프로틴 — 프로틴 특유의 맛없이 달콤하고 맛있게 영양을 보충함</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>선물용으로 우수한 패키지 — 상자 포장이 예쁘고 큼직하여 선물이나 경품용으로 적합함</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -3917,7 +3723,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 8입(7+1) - 추석 기프트 에디션 (공식수입)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 8입(7+1) - 스페셜 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -4010,25 +3816,25 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16143</v>
+        <v>16145</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>15477</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3369</v>
+        <v>3370</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>796</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1691</v>
+        <v>1693</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>214</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>8729</v>
+        <v>8728</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>779</v>
@@ -4040,80 +3846,24 @@
         <v>772</v>
       </c>
     </row>
-    <row r="8" ht="90" customHeight="1">
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>선물용으로 높은 만족도 — 명절이나 생일 선물로 주고받기에 매우 적절함
-우수한 피로 회복 효과 — 섭취 후 피로가 해소되고 체력이 보충되는 느낌을 받음
-신속한 배송 서비스 — 주문 후 배송이 빠르게 진행되어 만족스러움</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>피로 회복 및 활력 증진 — 피곤할 때 먹으면 체력이 회복되고 활력이 생김
-고급스러운 포장 디자인 — 포장과 패키지가 예쁘고 고급스러워 선물용으로 적합함
-간편한 휴대 및 섭취 — 하나씩 들고 다니며 부담 없이 먹기 편리함</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>체력 보충 및 피로 개선 — 마시고 나면 피로가 줄고 일상에 활력이 생김
-쿠폰 적용을 통한 할인 — 할인 쿠폰을 활용하여 합리적인 가격에 구매함</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>체력 유지 및 피로 회복 — 활동량이 많거나 육아 시 섭취하면 체력 유지에 큰 도움이 됨
-편리한 개별 포장 방식 — 한 포씩 포장되어 가방이나 책상에 두고 챙겨 먹기 용이함</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>품격 있는 고급 포장 — 패키지와 용기 포장이 품격 있어서 선물받을 때 기분이 좋음
-액상형의 편리한 섭취 — 액상 제형으로 알약보다 마시기 편리함
-빠른 피로 회복 효과 — 복용 시 피로가 풀리고 일상 에너지 보충에 효과적임</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>피로 개선 및 활력 보충 — 꾸준히 섭취하면 피로가 덜하고 활력 체감에 도움이 됨
-정성스러운 선물 패키징 — 패키지 구성이 정성스러워 생일이나 명절 선물용으로 만족함</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>물 없이 간편한 섭취 — 액상과 정제가 함께 있어 물 없이도 간편하게 먹을 수 있음
-에너지 충전과 상큼한 맛 — 오렌지 맛으로 맛있으며 섭취 후 에너지가 생김
-깔끔하고 예쁜 패키지 — 포장 케이스와 패키지가 예뻐 선물용으로 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>넉넉한 용량과 알찬 구성 — 한 달 동안 먹을 수 있는 넉넉한 수량과 구성이 만족스러움
-선물용 쇼핑백 기본 제공 — 쇼핑백이 함께 포함되어 명절 선물로 전달하기 용이함
-빠른 배송 서비스 — 연휴 기간임에도 차질 없이 빠르게 배송됨</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>맛있는 구미 젤리 제형 — 마이구미처럼 맛있고 쫄깃한 젤리라 거부감 없이 먹기 좋음
-물 없이 편리한 섭취 — 알약을 잘 못 먹는 사람도 물 없이 편하게 챙겨 먹음
-귀엽고 깔끔한 포장 — 포장이 귀엽고 깔끔하여 부담 없이 선물하기에 적합함</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>남녀 맞춤 옵션 선택 — 바이탈 m/f 중 성별에 맞게 선택할 수 있어 유용함
-꾸준한 활력 유지 효과 — 꾸준히 복용 시 피로가 줄고 활력이 오래 유지됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4121,31 +3871,14 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>동봉 쇼핑백 상태 불량 — 함께 제공된 선물용 쇼핑백이 훼손되어 도착함</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>배송 요청사항 미반영 — 관리실 위탁 요청에도 불구하고 문 앞에 배송되어 아쉬움</t>
-        </is>
-      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>상자 및 쇼핑백 오염 — 배송된 상자와 쇼핑백에 먼지가 가득 묻어 손질이 필요함
-봉인 스티커 훼손 문제 — 밀봉 스티커가 반쯤 떼어져 있고 손자국과 이물질이 묻어 있음</t>
-        </is>
-      </c>
+      <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>알약 크기로 인한 목넘김 — 기존 제품에 비해 알약 크기가 다소 커서 삼키기 부담스러움</t>
-        </is>
-      </c>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -4363,27 +4096,27 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
           <t>피부/미용</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -4415,32 +4148,32 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
           <t>셀렉스</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>알디콤</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>아일로</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>알디콤</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>타이거모닝</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>익스트림</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>익스트림</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -4472,32 +4205,32 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
+          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
           <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>아일로 타입1 콜라겐 비오틴 앰플 14일분 오간자 에디션 (고급 오간자 패키징 + 선물용 쇼핑백)</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>[좋은 아침 선물] 진저샷 미니보틀 8개입 (메시지 참 증정)</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -4553,106 +4286,49 @@
         <v>745</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F19" s="3" t="n">
+        <v>151</v>
+      </c>
+      <c r="G19" s="3" t="n">
         <v>215</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="H19" s="3" t="n">
+        <v>1534</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="J19" s="3" t="n">
         <v>759</v>
       </c>
-      <c r="H19" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="I19" s="3" t="n">
+      <c r="K19" s="3" t="n">
         <v>11</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>1534</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>248</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="20" ht="90" customHeight="1">
+    <row r="20">
       <c r="B20" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>고급스러운 포장 디자인 — 보자기, 틴케이스 등 고급스러운 포장으로 선물 가치가 높음
-비리지 않고 맛있는 풍미 — 콜라겐 특유의 비린 맛이 전혀 없고 맛있게 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>속이 편안한 소화 개선 — 식후 복용 시 속이 편안해지고 소화 및 배변에 도움이 됨
-고소하고 부담 없는 맛 — 고구마 맛 등으로 거부감 없이 맛있게 먹기 좋음
-다양한 증정품과 혜택 — 라이브 방송 구매 시 사은품 구성과 가격 혜택이 우수함</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>식후 더부룩함 완화 — 식사 후 복용하면 더부룩한 속이 가라앉고 편안해짐
-고소하고 맛있는 말차 맛 — 말차 맛이 고소하고 맛있어서 매일 챙겨 먹기 수월함</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>비리지 않고 달콤한 맛 — 단백질 음료 특유의 비린 맛과 텁텁함이 없고 달콤함
-운동 후 든든한 포만감 — 운동 후 섭취 시 영양 보충과 함께 가볍게 허기를 달래줌
-휴대하기 편한 슬림 용기 — 슬림한 팩 형태로 가방에 넣고 다니며 마시기 편함</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>화려하고 고급스러운 포장 — 오간자 패키지와 디자인이 고급스러워 선물받을 때 기분이 좋음
-상큼하고 부담 없는 맛 — 새콤상큼한 맛으로 맛에 대한 거부감 없이 마시기 좋음</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>우수한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 숙취와 무거운 컨디션이 개선됨
-간편한 스틱형 휴대성 — 물 없이 바로 먹는 스틱 포장이라 외출 시 지참하기 편함
-고급스러운 보라색 포장 — 패키지 포장이 고급스러워 지인 선물용으로 적합함</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>아침 활력과 에너지 충전 — 공복이나 아침 섭취 시 눈이 뜨이고 피로가 가시는 느낌을 받음
-과일이 들어간 상큼한 맛 — 과일 성분이 함유되어 생강 특유의 강한 맛없이 상큼하게 마심
-귀여운 미니 보틀 용기 — 용기 병이 작고 귀여워 손이 잘 가고 기분 전환에 도움 됨</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>아르기닌 밀크씨슬 조합 — 활력과 간 건강을 동시에 챙길 수 있는 2개월 세트 구성임
-체감되는 활력 증진 효과 — 아침 일어날 때 컨디션이 가볍고 운동 시 집중력이 좋아짐
-선물용 쇼핑백 증정 — 쇼핑백이 기본 동봉되어 주변에 선물하기에 용이함</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>6200mg 초고함량 활력 — 고함량 섭취로 운동 퍼포먼스 향상과 활력 유지에 도움을 줌
-간편한 하루 1포 포장 — 개별 포장된 스틱 제형이라 언제든 들고 다니며 섭취 가능함
-고급스러운 전용 쇼핑백 — 블랙과 레드 디자인 및 전용 쇼핑백이 제공되어 선물용으로 우수함</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>12종의 알찬 종합 구성 — 드링크, 쿠키, 바 등 베스트 12종을 다양하게 체험할 수 있음
-달콤하고 맛있는 프로틴 — 프로틴 특유의 맛없이 달콤하고 맛있게 영양을 보충함
-선물용으로 우수한 패키지 — 상자 포장이 예쁘고 큼직하여 선물이나 경품용으로 적합함</t>
-        </is>
-      </c>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="B21" s="1" t="inlineStr">
@@ -4660,23 +4336,11 @@
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>다소 높은 가격대 — 가격이 비싼 편이며 꾸준히 인상되어 구매 부담이 있음</t>
-        </is>
-      </c>
+      <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>다소 느린 배송 처리 — 주문 후 배송받기까지 시간이 다소 걸려 아쉬움</t>
-        </is>
-      </c>
+      <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>단기 복용 시 미미한 효과 — 단기간 섭취로는 피부 효과를 즉각 느끼기 어려움</t>
-        </is>
-      </c>
+      <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
@@ -4706,32 +4370,32 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
+          <t>45,800원</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
           <t>28,900원</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>25,900원</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>33,200원</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>32,900원</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>33,200원</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>29,900원</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>25,900원</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>43,900원</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -4934,47 +4598,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 10정 10일분</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>1,500원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000278&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260504/uooE7Z5tFnMjhhremBna600000278_00_01uooE7Z5tFnMjhhremBna.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>726</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>부담 없는 10일분 소량 — 10정 소용량으로 구성되어 부담 없이 구매하여 시도해보기 좋음</t>
-        </is>
-      </c>
+        <v>788</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>복용 시점 안내의 부족 — 식전 또는 식후 섭취 시점에 대한 구체적인 설명이 부족함</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
@@ -4989,12 +4645,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CJ 카무트 곡물과채콤부 화사 효소 10포 10일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CJ웰케어</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5004,30 +4660,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=139213437&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260623/2v2CuiCUbhEwDNpboF5B139213437_00_002v2CuiCUbhEwDNpboF5B.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>1234</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>빠르고 확실한 소화 개선 — 식사 후나 과식 시 섭취하면 속이 편안해지고 소화가 잘됨</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>높은 가성비와 편리함 — 저렴한 가격에 구매 가능하며 사용하기에 편리함</t>
-        </is>
-      </c>
+        <v>2733</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -5036,7 +4684,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5044,10 +4692,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>광동 위생천 10개입</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>오브맘 다이어트 홀릭 30포 15일분</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>오브맘</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>5,000원</t>
@@ -5055,31 +4707,23 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600200240&amp;recmYn=N</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624075&amp;recmYn=N</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250519/2rLyPRrrXXN6XdvBMjj5913624075_00_002rLyPRrrXXN6XdvBMjj5.jpg</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
-        <v>404</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>우수한 소화 촉진 효과 — 더부룩할 때 마시면 속이 빠르게 시원해지고 소화가 잘됨</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>약국 대비 저렴한 가격 — 약국보다 훨씬 저렴하여 가성비가 매우 뛰어남</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>상비약 구비의 적합성 — 가정이나 사무실에 상비해 두고 필요할 때 챙겨 마시기 좋음</t>
-        </is>
-      </c>
+        <v>1043</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -5087,7 +4731,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5095,12 +4739,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 비타민B 30정 30일분</t>
+          <t>[식후 혈당] 동화 배러크런치 바나바 요구르트맛 30정 10일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5110,43 +4754,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000129&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601678608&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5QghHD5oyZssCfnGZbzA600000129_00_005QghHD5oyZssCfnGZbzA.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260825/oxNqPxCfU3Tre5j0PQQk601678608_00_02oxNqPxCfU3Tre5j0PQQk.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>2230</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>목넘김이 편한 알약 크기 — 알약 크기가 크지 않아서 수월하게 삼킬 수 있음</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>부담 없는 일상 가성비 — 매일 출근 시 챙겨 먹기에 가격 부담이 없음</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>용량 대비 아쉬운 함량 — 고함량 제품에 비해 함량 면에서 다소 아쉽다고 느낌</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5154,7 +4786,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민 미네랄 츄어블 60정 30일분</t>
+          <t>대웅제약 바나바잎 10정 10일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5164,41 +4796,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000142&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000278&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/CJUce0AJqtqHn7R3ZFm1600000142_00_00CJUce0AJqtqHn7R3ZFm1.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/uooE7Z5tFnMjhhremBna600000278_00_01uooE7Z5tFnMjhhremBna.png</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>608</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>씹어먹는 편리한 츄어블 — 알약을 삼키기 어려워하는 사람도 쉽게 씹어서 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>아이들의 높은 섭취도 — 맛이 우수하여 어린아이들도 거부감 없이 잘 먹음</t>
-        </is>
-      </c>
+        <v>726</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>효과 체감의 다소 미흡 — 꾸준히 복용하고 있으나 즉각적인 효과 체감은 다소 미흡함</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -5213,45 +4833,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>종근당건강 락토핏 골드</t>
+          <t>[혈액 생성] 동화약품 배러크런치 철분 사과맛 30정 10일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580521&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601678607&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260522/0jgRGoNZEcwwrbTgrqVw591580521_00_000jgRGoNZEcwwrbTgrqVw.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260825/1a3CLvRrBJMActwA3NW5601678607_00_021a3CLvRrBJMActwA3NW5.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1638</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>필요 수량 저렴하게 구매 — 필요한 만큼 소량으로 싸게 구매할 수 있어 만족스러움</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>꾸준히 복용하기 용이함 — 기초 유산균으로 부담 없이 매일 챙겨 먹기 적절함</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -5260,7 +4872,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5268,58 +4880,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>종근당건강 브이퍼센트 멀티비타민 콜라겐샷 5포</t>
+          <t>[항산화] 동화약품 배러크런치C 레몬맛 30정 10일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591591420&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601678604&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250514/oMFpSUTevplZ5wvdXiLh591591420_00_00oMFpSUTevplZ5wvdXiLh.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260825/GVr6GsoojIJO6UtcBMHG601678604_00_02GVr6GsoojIJO6UtcBMHG.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>268</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>맛있고 편리한 복용감 — 맛이 좋아서 피부 관리를 위해 편리하게 마실 수 있음</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>당 성분 함유의 아쉬움 — 당 성분이 포함되어 있어 매일 섭취 시 아쉽게 느껴짐</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>생소한 섭취 방법 — 처음 섭취할 때 어떻게 먹어야 할지 약간 당황스러움</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5327,50 +4927,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>오브맘 비타민C＆E 하루구미 30일분</t>
+          <t>[정상 면역] 동화약품 배러크런치 아연 청포도맛 30정 10일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602131&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601678606&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250922/jrLxfLkWCczsCAsnqLoJ613602131_00_01jrLxfLkWCczsCAsnqLoJ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260825/9arKLwQMyanllW5dsWAc601678606_00_029arKLwQMyanllW5dsWAc.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>973</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>자극 없는 쫄깃한 젤리 — 강한 신맛 없이 쫄깃하고 맛있어서 간식처럼 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>저렴하고 뛰어난 가성비 — 저렴한 가격에 구미 형태로 영양을 챙길 수 있어 만족함</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>언제 어디서나 간편 섭취 — 젤리 형태라 물이 없어도 언제든 편하게 복용함</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -5413,24 +5001,12 @@
         <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>888</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>매우 저렴한 가격대 — 가격이 매우 저렴하여 부담 없이 다이어트 보조제로 구매 가능함</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>꾸준한 복용 시의 효과 — 꾸준히 매일 챙겨 먹었을 때 컨디션 유지에 유용함을 느낌</t>
-        </is>
-      </c>
+        <v>892</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>붓기 개선 효과 부재 — 식후 복용에도 불구하고 붓기 감소 효과를 체감하지 못함</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -5445,50 +5021,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[보령약국 X Pantio] 스트레스 케어 올인원 15포 15일분</t>
+          <t>홀베리 레몬 비타C 500 10개입</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>판티오</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033991022&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=030086178&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260805/bpRaPOFB6GapUUiby4Vv033991022_00_00bpRaPOFB6GapUUiby4Vv.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260922/2diYV2S85V8WH0UA5lRP030086178_00_002diYV2S85V8WH0UA5lRP.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
-        <v>79</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>숙면 및 불면증 완화 — 취침 전 섭취 시 밤에 잠이 잘 오고 수면에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>간편한 일상 섭취 — 포 형태로 되어 있어 꼬박꼬박 챙겨 먹기 수월함</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>만족스러운 가성비 — 가격 대비 만족도가 높아 지속적인 구매 의사가 생김</t>
-        </is>
-      </c>
+        <v>859</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -5614,32 +5178,32 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -5661,38 +5225,42 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>닥터블릿</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>오브맘</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>동화약품</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>CJ웰케어</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -5702,7 +5270,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>판티오</t>
+          <t>홀베리</t>
         </is>
       </c>
     </row>
@@ -5714,42 +5282,42 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>오브맘 다이어트 홀릭 30포 15일분</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[식후 혈당] 동화 배러크런치 바나바 요구르트맛 30정 10일분</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
           <t>대웅제약 바나바잎 10정 10일분</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>CJ 카무트 곡물과채콤부 화사 효소 10포 10일분</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>광동 위생천 10개입</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 비타민B 30정 30일분</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 멀티비타민 미네랄 츄어블 60정 30일분</t>
-        </is>
-      </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>종근당건강 락토핏 골드</t>
+          <t>[혈액 생성] 동화약품 배러크런치 철분 사과맛 30정 10일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>종근당건강 브이퍼센트 멀티비타민 콜라겐샷 5포</t>
+          <t>[항산화] 동화약품 배러크런치C 레몬맛 30정 10일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 비타민C＆E 하루구미 30일분</t>
+          <t>[정상 면역] 동화약품 배러크런치 아연 청포도맛 30정 10일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -5759,7 +5327,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[보령약국 X Pantio] 스트레스 케어 올인원 15포 15일분</t>
+          <t>홀베리 레몬 비타C 500 10개입</t>
         </is>
       </c>
     </row>
@@ -5773,13 +5341,13 @@
         <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>4.8</v>
@@ -5797,7 +5365,7 @@
         <v>4.7</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="7">
@@ -5807,140 +5375,68 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
+        <v>788</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>2733</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1043</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>726</v>
       </c>
-      <c r="D7" s="3" t="n">
-        <v>1234</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>404</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>2230</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>608</v>
-      </c>
       <c r="H7" s="3" t="n">
-        <v>1638</v>
+        <v>42</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>268</v>
+        <v>33</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>973</v>
+        <v>33</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>부담 없는 10일분 소량 — 10정 소용량으로 구성되어 부담 없이 구매하여 시도해보기 좋음</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>빠르고 확실한 소화 개선 — 식사 후나 과식 시 섭취하면 속이 편안해지고 소화가 잘됨
-높은 가성비와 편리함 — 저렴한 가격에 구매 가능하며 사용하기에 편리함</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>우수한 소화 촉진 효과 — 더부룩할 때 마시면 속이 빠르게 시원해지고 소화가 잘됨
-약국 대비 저렴한 가격 — 약국보다 훨씬 저렴하여 가성비가 매우 뛰어남
-상비약 구비의 적합성 — 가정이나 사무실에 상비해 두고 필요할 때 챙겨 마시기 좋음</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>목넘김이 편한 알약 크기 — 알약 크기가 크지 않아서 수월하게 삼킬 수 있음
-부담 없는 일상 가성비 — 매일 출근 시 챙겨 먹기에 가격 부담이 없음</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>씹어먹는 편리한 츄어블 — 알약을 삼키기 어려워하는 사람도 쉽게 씹어서 먹을 수 있음
-아이들의 높은 섭취도 — 맛이 우수하여 어린아이들도 거부감 없이 잘 먹음</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>필요 수량 저렴하게 구매 — 필요한 만큼 소량으로 싸게 구매할 수 있어 만족스러움
-꾸준히 복용하기 용이함 — 기초 유산균으로 부담 없이 매일 챙겨 먹기 적절함</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>맛있고 편리한 복용감 — 맛이 좋아서 피부 관리를 위해 편리하게 마실 수 있음</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>자극 없는 쫄깃한 젤리 — 강한 신맛 없이 쫄깃하고 맛있어서 간식처럼 먹기 좋음
-저렴하고 뛰어난 가성비 — 저렴한 가격에 구미 형태로 영양을 챙길 수 있어 만족함
-언제 어디서나 간편 섭취 — 젤리 형태라 물이 없어도 언제든 편하게 복용함</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>매우 저렴한 가격대 — 가격이 매우 저렴하여 부담 없이 다이어트 보조제로 구매 가능함
-꾸준한 복용 시의 효과 — 꾸준히 매일 챙겨 먹었을 때 컨디션 유지에 유용함을 느낌</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>숙면 및 불면증 완화 — 취침 전 섭취 시 밤에 잠이 잘 오고 수면에 도움을 줌
-간편한 일상 섭취 — 포 형태로 되어 있어 꼬박꼬박 챙겨 먹기 수월함
-만족스러운 가성비 — 가격 대비 만족도가 높아 지속적인 구매 의사가 생김</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>복용 시점 안내의 부족 — 식전 또는 식후 섭취 시점에 대한 구체적인 설명이 부족함</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>용량 대비 아쉬운 함량 — 고함량 제품에 비해 함량 면에서 다소 아쉽다고 느낌</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>효과 체감의 다소 미흡 — 꾸준히 복용하고 있으나 즉각적인 효과 체감은 다소 미흡함</t>
-        </is>
-      </c>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>당 성분 함유의 아쉬움 — 당 성분이 포함되어 있어 매일 섭취 시 아쉽게 느껴짐
-생소한 섭취 방법 — 처음 섭취할 때 어떻게 먹어야 할지 약간 당황스러움</t>
-        </is>
-      </c>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>붓기 개선 효과 부재 — 식후 복용에도 불구하고 붓기 감소 효과를 체감하지 못함</t>
-        </is>
-      </c>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
@@ -5951,42 +5447,42 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>1,500원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
           <t>1,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -5996,7 +5492,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
     </row>
@@ -6175,7 +5671,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6183,27 +5679,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>뉴트리엘 이너포뮬러 샐그린 27 60정 (1개월분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>뉴트리엘</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20,900원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000257982&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025798204ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -6218,7 +5714,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6226,50 +5722,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31,900원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J3" t="n">
-        <v>8265</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>60캡슐 2개월분 기획 — 더블 기획 세트로 두 달 동안 충분히 복용 가능한 구성임</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>공복 섭취 시 편안함 — 아침 공복에 물과 함께 간편하게 1캡슐씩 챙기기 좋음</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>여성 건강 이너케어 — 질 건강을 함께 챙길 수 있는 유산균으로 유용함</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -6277,7 +5757,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6285,27 +5765,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>딥트3일</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16,000원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000211396&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021139617ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -6320,7 +5800,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6328,27 +5808,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>빌드</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000219379&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021937922ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -6363,7 +5843,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6371,27 +5851,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[행자PICK/공구특가] 락티브 이노시톨 탱글 젤리/컬리케일/이노시톨 기획세트(+질유래 유산균 10캡슐)</t>
+          <t>[9월 올영픽/산리오콜라보] CJ 이너비 브이 캔디 14포 (+마이멜로디 마그넷액자)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>락티브</t>
+          <t>CJ이너비</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>9,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=B000000244315&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000264048&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/B00000024431506ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026404810ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -6406,7 +5886,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6414,27 +5894,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[추성훈 PICK] 헬스헬퍼 맥스컷 프로 크롬 60캡슐 (10일분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>헬스헬퍼</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>39,800원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000237482&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023748215ko.png?l=ko</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -6449,7 +5929,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6457,27 +5937,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -6492,7 +5972,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6500,50 +5980,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>씨제이웰케어</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,900원</t>
+          <t>39,800원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J9" t="n">
-        <v>18817</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>부담 없는 뛰어난 가성비 — 가격이 매우 저렴하여 장기 복용에 대한 경제적 부담이 없음</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>위생적인 개별 포장 — 개별 포장이 되어 있어 위생적이고 외출이나 여행 시 휴대하기 편함</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>하루 한 알 영양 관리 — 한 알로 비타민과 미네랄을 한 번에 보충하여 간편함</t>
-        </is>
-      </c>
+        <v>522</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -6559,58 +6027,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>13,950원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014345ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>26861</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>배변 활동 및 속 편안함 — 섭취 시 화장실을 잘 가고 더부룩했던 뱃살 감소에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>식후 체지방 관리 효과 — 과식 후나 일상에서 체지방 관리를 꾸준히 하기에 적절함</t>
-        </is>
-      </c>
+        <v>12762</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>알약의 다소 큰 크기 — 알약 크기가 조금 큰 편이라 삼킬 때 목넘김이 다소 아쉬움</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6618,50 +6074,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[올영단독] 지노마스터 질유산균 70캡슐 (70일분)</t>
+          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>59,000원</t>
+          <t>18,800원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000249509&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024950901ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364590ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>391</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>질과 장 동시 더블케어 — 질 건강과 장 건강을 유산균 한 포로 동시에 관리 가능함</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>작은 캡슐의 수월한 목넘김 — 캡슐 크기가 작아 바쁜 아침에도 목넘김에 부담이 없음</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>70일분의 넉넉한 용량 — 70캡슐 구성으로 오랜 기간 챙겨 먹기 적절함</t>
-        </is>
-      </c>
+        <v>17163</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -6777,44 +6221,44 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
@@ -6822,7 +6266,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -6834,52 +6278,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>뉴트리엘</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>딥트3일</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>빌드</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>락티브</t>
+          <t>CJ이너비</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
+          <t>헬스헬퍼</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>프로뉴트리션</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>씨제이웰케어</t>
-        </is>
-      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
+          <t>바이오코어유산균</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>푸드올로지</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
         </is>
       </c>
     </row>
@@ -6891,52 +6335,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>뉴트리엘 이너포뮬러 샐그린 27 60정 (1개월분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>[행자PICK/공구특가] 락티브 이노시톨 탱글 젤리/컬리케일/이노시톨 기획세트(+질유래 유산균 10캡슐)</t>
+          <t>[9월 올영픽/산리오콜라보] CJ 이너비 브이 캔디 14포 (+마이멜로디 마그넷액자)</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
+          <t>[추성훈 PICK] 헬스헬퍼 맥스컷 프로 크롬 60캡슐 (10일분)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
-        </is>
-      </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[올영단독] 지노마스터 질유산균 70캡슐 (70일분)</t>
+          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
     </row>
@@ -6947,22 +6391,20 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="n">
-        <v>4.9</v>
-      </c>
+      <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="K6" s="3" t="n">
-        <v>4.7</v>
-      </c>
       <c r="L6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -6972,63 +6414,38 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="n">
-        <v>8265</v>
-      </c>
+      <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="n">
-        <v>18817</v>
+        <v>522</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>26861</v>
+        <v>12762</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>17163</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>60캡슐 2개월분 기획 — 더블 기획 세트로 두 달 동안 충분히 복용 가능한 구성임
-공복 섭취 시 편안함 — 아침 공복에 물과 함께 간편하게 1캡슐씩 챙기기 좋음
-여성 건강 이너케어 — 질 건강을 함께 챙길 수 있는 유산균으로 유용함</t>
-        </is>
-      </c>
+      <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="3" t="inlineStr"/>
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>부담 없는 뛰어난 가성비 — 가격이 매우 저렴하여 장기 복용에 대한 경제적 부담이 없음
-위생적인 개별 포장 — 개별 포장이 되어 있어 위생적이고 외출이나 여행 시 휴대하기 편함
-하루 한 알 영양 관리 — 한 알로 비타민과 미네랄을 한 번에 보충하여 간편함</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>배변 활동 및 속 편안함 — 섭취 시 화장실을 잘 가고 더부룩했던 뱃살 감소에 도움을 줌
-식후 체지방 관리 효과 — 과식 후나 일상에서 체지방 관리를 꾸준히 하기에 적절함</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>질과 장 동시 더블케어 — 질 건강과 장 건강을 유산균 한 포로 동시에 관리 가능함
-작은 캡슐의 수월한 목넘김 — 캡슐 크기가 작아 바쁜 아침에도 목넘김에 부담이 없음
-70일분의 넉넉한 용량 — 70캡슐 구성으로 오랜 기간 챙겨 먹기 적절함</t>
-        </is>
-      </c>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -7044,11 +6461,7 @@
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>알약의 다소 큰 크기 — 알약 크기가 조금 큰 편이라 삼킬 때 목넘김이 다소 아쉬움</t>
-        </is>
-      </c>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
@@ -7059,52 +6472,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>20,900원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>31,900원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>16,000원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
+          <t>17,900원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>9,900원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
           <t>18,900원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>25,900원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>39,800원</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>16,900원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,900원</t>
-        </is>
-      </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>13,950원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>59,000원</t>
+          <t>18,800원</t>
         </is>
       </c>
     </row>
@@ -7234,63 +6647,63 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>32.5</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7300,10 +6713,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -7312,7 +6725,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -7340,29 +6753,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7372,10 +6785,10 @@
         <v>2.5</v>
       </c>
       <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
         <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
